--- a/MaxMinMeanSD.xlsx
+++ b/MaxMinMeanSD.xlsx
@@ -416,7 +416,7 @@
         <v>17.345971563981</v>
       </c>
       <c r="E2" t="n">
-        <v>6.19043155419602</v>
+        <v>6.19043155419603</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +433,7 @@
         <v>12.9869668246445</v>
       </c>
       <c r="E3" t="n">
-        <v>4.79210212184893</v>
+        <v>4.79210212184894</v>
       </c>
     </row>
     <row r="4">
@@ -450,7 +450,7 @@
         <v>0.859004739336493</v>
       </c>
       <c r="E4" t="n">
-        <v>0.348223016548168</v>
+        <v>0.348223016548167</v>
       </c>
     </row>
     <row r="5">
@@ -498,7 +498,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.657582938388626</v>
+        <v>0.657582938388625</v>
       </c>
       <c r="E7" t="n">
         <v>2.15255688651815</v>
@@ -535,7 +535,7 @@
         <v>0.39010663507109</v>
       </c>
       <c r="E9" t="n">
-        <v>0.646181309831365</v>
+        <v>0.646181309831362</v>
       </c>
     </row>
     <row r="10">
@@ -552,7 +552,7 @@
         <v>36.3590047393365</v>
       </c>
       <c r="E10" t="n">
-        <v>7.09687428598372</v>
+        <v>7.09687428598373</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>4.17890995260664</v>
+        <v>4.17890995260663</v>
       </c>
       <c r="E11" t="n">
-        <v>2.47118257002047</v>
+        <v>2.47118257002046</v>
       </c>
     </row>
   </sheetData>
